--- a/libertadores/datasets_liberta/confrontos_fase_1_libertadores.xlsx
+++ b/libertadores/datasets_liberta/confrontos_fase_1_libertadores.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="248" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="488" uniqueCount="80">
   <si>
     <t>Grupo</t>
   </si>
@@ -40,112 +40,220 @@
     <t>Visitante_ID_Time</t>
   </si>
   <si>
-    <t>Grupo I</t>
-  </si>
-  <si>
-    <t>Grupo J</t>
-  </si>
-  <si>
-    <t>Grupo K</t>
-  </si>
-  <si>
-    <t>Grupo L</t>
-  </si>
-  <si>
-    <t>1_I</t>
-  </si>
-  <si>
-    <t>3_I</t>
-  </si>
-  <si>
-    <t>1_J</t>
-  </si>
-  <si>
-    <t>3_J</t>
-  </si>
-  <si>
-    <t>1_K</t>
-  </si>
-  <si>
-    <t>3_K</t>
-  </si>
-  <si>
-    <t>1_L</t>
-  </si>
-  <si>
-    <t>3_L</t>
-  </si>
-  <si>
-    <t>2_I</t>
-  </si>
-  <si>
-    <t>4_I</t>
-  </si>
-  <si>
-    <t>2_J</t>
-  </si>
-  <si>
-    <t>4_J</t>
-  </si>
-  <si>
-    <t>2_K</t>
-  </si>
-  <si>
-    <t>4_K</t>
-  </si>
-  <si>
-    <t>2_L</t>
-  </si>
-  <si>
-    <t>4_L</t>
+    <t>Grupo A</t>
+  </si>
+  <si>
+    <t>Grupo B</t>
+  </si>
+  <si>
+    <t>Grupo C</t>
+  </si>
+  <si>
+    <t>Grupo D</t>
+  </si>
+  <si>
+    <t>Grupo E</t>
+  </si>
+  <si>
+    <t>Grupo F</t>
+  </si>
+  <si>
+    <t>Grupo G</t>
+  </si>
+  <si>
+    <t>Grupo H</t>
+  </si>
+  <si>
+    <t>4_A</t>
+  </si>
+  <si>
+    <t>3_A</t>
+  </si>
+  <si>
+    <t>4_B</t>
+  </si>
+  <si>
+    <t>3_B</t>
+  </si>
+  <si>
+    <t>4_C</t>
+  </si>
+  <si>
+    <t>3_C</t>
+  </si>
+  <si>
+    <t>4_D</t>
+  </si>
+  <si>
+    <t>3_D</t>
+  </si>
+  <si>
+    <t>4_E</t>
+  </si>
+  <si>
+    <t>3_E</t>
+  </si>
+  <si>
+    <t>3_F</t>
+  </si>
+  <si>
+    <t>1_F</t>
+  </si>
+  <si>
+    <t>4_G</t>
+  </si>
+  <si>
+    <t>3_G</t>
+  </si>
+  <si>
+    <t>4_H</t>
+  </si>
+  <si>
+    <t>3_H</t>
+  </si>
+  <si>
+    <t>1_A</t>
+  </si>
+  <si>
+    <t>2_A</t>
+  </si>
+  <si>
+    <t>1_B</t>
+  </si>
+  <si>
+    <t>2_B</t>
+  </si>
+  <si>
+    <t>1_C</t>
+  </si>
+  <si>
+    <t>2_C</t>
+  </si>
+  <si>
+    <t>1_D</t>
+  </si>
+  <si>
+    <t>2_D</t>
+  </si>
+  <si>
+    <t>1_E</t>
+  </si>
+  <si>
+    <t>2_E</t>
+  </si>
+  <si>
+    <t>4_F</t>
+  </si>
+  <si>
+    <t>2_F</t>
+  </si>
+  <si>
+    <t>1_G</t>
+  </si>
+  <si>
+    <t>2_G</t>
+  </si>
+  <si>
+    <t>1_H</t>
+  </si>
+  <si>
+    <t>2_H</t>
+  </si>
+  <si>
+    <t>SERGRILLO</t>
+  </si>
+  <si>
+    <t>JUV. KP</t>
+  </si>
+  <si>
+    <t>S.E.R. GRILLO</t>
+  </si>
+  <si>
+    <t>LISI GREMISTA</t>
+  </si>
+  <si>
+    <t>seralex</t>
+  </si>
+  <si>
+    <t>Bandoleros FCS</t>
+  </si>
+  <si>
+    <t>Mau Humor F.C.</t>
+  </si>
+  <si>
+    <t>Grêmio imortal 36</t>
+  </si>
+  <si>
+    <t>Fedato Futebol Clube</t>
+  </si>
+  <si>
+    <t>FÚRIA LEON</t>
+  </si>
+  <si>
+    <t>AZURRA82</t>
+  </si>
+  <si>
+    <t>DM Studio</t>
+  </si>
+  <si>
+    <t>A Lenda Super Vascão f.c</t>
+  </si>
+  <si>
+    <t>TORRESMO COM PINGA PRO26.1</t>
+  </si>
+  <si>
+    <t>Super Vasco f.c</t>
+  </si>
+  <si>
+    <t>Texas Club 2026</t>
+  </si>
+  <si>
+    <t>Tatols Beants F.C</t>
   </si>
   <si>
     <t>JV5 Tricolor Gaúcho</t>
   </si>
   <si>
-    <t>Bandoleros FCS</t>
-  </si>
-  <si>
     <t>Dom Camillo68</t>
   </si>
   <si>
+    <t>Máquina Laranjja</t>
+  </si>
+  <si>
+    <t>cartola scheuer17</t>
+  </si>
+  <si>
+    <t>dasdoresfc</t>
+  </si>
+  <si>
     <t>A Lenda Super Vasco F.c</t>
   </si>
   <si>
-    <t>Fedato Futebol Clube</t>
-  </si>
-  <si>
-    <t>TORRESMO COM PINGA PRO26.1</t>
+    <t>FBC Colorado</t>
+  </si>
+  <si>
+    <t>KillerColorado</t>
+  </si>
+  <si>
+    <t>Paulo Virgili FC</t>
   </si>
   <si>
     <t>lsauer fc</t>
   </si>
   <si>
-    <t>Texas Club 2026</t>
-  </si>
-  <si>
-    <t>LISI GREMISTA</t>
-  </si>
-  <si>
-    <t>Mau Humor F.C.</t>
-  </si>
-  <si>
-    <t>Tatols Beants F.C</t>
-  </si>
-  <si>
-    <t>cartola scheuer17</t>
-  </si>
-  <si>
-    <t>DM Studio</t>
+    <t>Rolo Compressor ZN</t>
+  </si>
+  <si>
+    <t>Grêmio imortal 37</t>
+  </si>
+  <si>
+    <t>Tabajara de Inhaua PB1</t>
   </si>
   <si>
     <t>TEAM LOPES 99</t>
   </si>
   <si>
-    <t>KillerColorado</t>
-  </si>
-  <si>
-    <t>Tabajara de Inhaua PB1</t>
+    <t>Gremiomaniasm</t>
   </si>
 </sst>
 </file>
@@ -503,7 +611,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H49"/>
+  <dimension ref="A1:H97"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
@@ -537,25 +645,25 @@
         <v>8</v>
       </c>
       <c r="B2" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="C2" t="s">
-        <v>20</v>
+        <v>33</v>
       </c>
       <c r="D2">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="E2" t="s">
-        <v>28</v>
+        <v>48</v>
       </c>
       <c r="F2">
+        <v>25811332</v>
+      </c>
+      <c r="G2" t="s">
+        <v>65</v>
+      </c>
+      <c r="H2">
         <v>1747619</v>
-      </c>
-      <c r="G2" t="s">
-        <v>36</v>
-      </c>
-      <c r="H2">
-        <v>51010813</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -563,25 +671,25 @@
         <v>8</v>
       </c>
       <c r="B3" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="C3" t="s">
-        <v>21</v>
+        <v>32</v>
       </c>
       <c r="D3">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="E3" t="s">
-        <v>29</v>
+        <v>49</v>
       </c>
       <c r="F3">
-        <v>13913874</v>
+        <v>13951133</v>
       </c>
       <c r="G3" t="s">
-        <v>37</v>
+        <v>64</v>
       </c>
       <c r="H3">
-        <v>19033717</v>
+        <v>212042</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -589,25 +697,25 @@
         <v>9</v>
       </c>
       <c r="B4" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="C4" t="s">
-        <v>22</v>
+        <v>35</v>
       </c>
       <c r="D4">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="E4" t="s">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="F4">
-        <v>20696550</v>
+        <v>5823700</v>
       </c>
       <c r="G4" t="s">
-        <v>38</v>
+        <v>67</v>
       </c>
       <c r="H4">
-        <v>212042</v>
+        <v>30267301</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -615,25 +723,25 @@
         <v>9</v>
       </c>
       <c r="B5" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="C5" t="s">
-        <v>23</v>
+        <v>34</v>
       </c>
       <c r="D5">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="E5" t="s">
-        <v>31</v>
+        <v>51</v>
       </c>
       <c r="F5">
-        <v>117598</v>
+        <v>51010813</v>
       </c>
       <c r="G5" t="s">
-        <v>39</v>
+        <v>66</v>
       </c>
       <c r="H5">
-        <v>3851966</v>
+        <v>20696550</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -641,25 +749,25 @@
         <v>10</v>
       </c>
       <c r="B6" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="C6" t="s">
-        <v>24</v>
+        <v>37</v>
       </c>
       <c r="D6">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="E6" t="s">
-        <v>32</v>
+        <v>52</v>
       </c>
       <c r="F6">
-        <v>18642587</v>
+        <v>29228373</v>
       </c>
       <c r="G6" t="s">
-        <v>40</v>
+        <v>69</v>
       </c>
       <c r="H6">
-        <v>387186</v>
+        <v>7017989</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -667,25 +775,25 @@
         <v>10</v>
       </c>
       <c r="B7" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="C7" t="s">
-        <v>25</v>
+        <v>36</v>
       </c>
       <c r="D7">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="E7" t="s">
-        <v>33</v>
+        <v>53</v>
       </c>
       <c r="F7">
-        <v>47544767</v>
+        <v>13913874</v>
       </c>
       <c r="G7" t="s">
-        <v>41</v>
+        <v>68</v>
       </c>
       <c r="H7">
-        <v>479510</v>
+        <v>3851966</v>
       </c>
     </row>
     <row r="8" spans="1:8">
@@ -693,25 +801,25 @@
         <v>11</v>
       </c>
       <c r="B8" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="C8" t="s">
-        <v>26</v>
+        <v>39</v>
       </c>
       <c r="D8">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="E8" t="s">
-        <v>34</v>
+        <v>54</v>
       </c>
       <c r="F8">
-        <v>44810918</v>
+        <v>19033717</v>
       </c>
       <c r="G8" t="s">
-        <v>42</v>
+        <v>71</v>
       </c>
       <c r="H8">
-        <v>36359</v>
+        <v>186283</v>
       </c>
     </row>
     <row r="9" spans="1:8">
@@ -719,233 +827,233 @@
         <v>11</v>
       </c>
       <c r="B9" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="C9" t="s">
-        <v>27</v>
+        <v>38</v>
       </c>
       <c r="D9">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="E9" t="s">
-        <v>35</v>
+        <v>55</v>
       </c>
       <c r="F9">
-        <v>1273719</v>
+        <v>24856400</v>
       </c>
       <c r="G9" t="s">
-        <v>43</v>
+        <v>70</v>
       </c>
       <c r="H9">
-        <v>28741323</v>
+        <v>117598</v>
       </c>
     </row>
     <row r="10" spans="1:8">
       <c r="A10" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="B10" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="C10" t="s">
-        <v>13</v>
+        <v>41</v>
       </c>
       <c r="D10">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="E10" t="s">
-        <v>36</v>
+        <v>56</v>
       </c>
       <c r="F10">
-        <v>51010813</v>
+        <v>18642587</v>
       </c>
       <c r="G10" t="s">
-        <v>29</v>
+        <v>73</v>
       </c>
       <c r="H10">
-        <v>13913874</v>
+        <v>14124559</v>
       </c>
     </row>
     <row r="11" spans="1:8">
       <c r="A11" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="B11" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="C11" t="s">
-        <v>12</v>
+        <v>40</v>
       </c>
       <c r="D11">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="E11" t="s">
-        <v>37</v>
+        <v>57</v>
       </c>
       <c r="F11">
-        <v>19033717</v>
+        <v>18344271</v>
       </c>
       <c r="G11" t="s">
-        <v>28</v>
+        <v>72</v>
       </c>
       <c r="H11">
-        <v>1747619</v>
+        <v>36359</v>
       </c>
     </row>
     <row r="12" spans="1:8">
       <c r="A12" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="B12" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="C12" t="s">
-        <v>15</v>
+        <v>42</v>
       </c>
       <c r="D12">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="E12" t="s">
-        <v>38</v>
+        <v>58</v>
       </c>
       <c r="F12">
-        <v>212042</v>
+        <v>18346776</v>
       </c>
       <c r="G12" t="s">
-        <v>31</v>
+        <v>74</v>
       </c>
       <c r="H12">
-        <v>117598</v>
+        <v>44810918</v>
       </c>
     </row>
     <row r="13" spans="1:8">
       <c r="A13" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="B13" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="C13" t="s">
-        <v>14</v>
+        <v>43</v>
       </c>
       <c r="D13">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="E13" t="s">
-        <v>39</v>
+        <v>59</v>
       </c>
       <c r="F13">
-        <v>3851966</v>
+        <v>387186</v>
       </c>
       <c r="G13" t="s">
-        <v>30</v>
+        <v>75</v>
       </c>
       <c r="H13">
-        <v>20696550</v>
+        <v>18223508</v>
       </c>
     </row>
     <row r="14" spans="1:8">
       <c r="A14" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="B14" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="C14" t="s">
-        <v>17</v>
+        <v>45</v>
       </c>
       <c r="D14">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="E14" t="s">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="F14">
-        <v>387186</v>
+        <v>49355335</v>
       </c>
       <c r="G14" t="s">
-        <v>33</v>
+        <v>77</v>
       </c>
       <c r="H14">
-        <v>47544767</v>
+        <v>28741323</v>
       </c>
     </row>
     <row r="15" spans="1:8">
       <c r="A15" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="C15" t="s">
-        <v>16</v>
+        <v>44</v>
       </c>
       <c r="D15">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="E15" t="s">
-        <v>41</v>
+        <v>61</v>
       </c>
       <c r="F15">
-        <v>479510</v>
+        <v>47544767</v>
       </c>
       <c r="G15" t="s">
-        <v>32</v>
+        <v>76</v>
       </c>
       <c r="H15">
-        <v>18642587</v>
+        <v>24468241</v>
       </c>
     </row>
     <row r="16" spans="1:8">
       <c r="A16" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="B16" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="C16" t="s">
-        <v>19</v>
+        <v>47</v>
       </c>
       <c r="D16">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="E16" t="s">
-        <v>42</v>
+        <v>62</v>
       </c>
       <c r="F16">
-        <v>36359</v>
+        <v>13707047</v>
       </c>
       <c r="G16" t="s">
-        <v>35</v>
+        <v>79</v>
       </c>
       <c r="H16">
-        <v>1273719</v>
+        <v>528730</v>
       </c>
     </row>
     <row r="17" spans="1:8">
       <c r="A17" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="B17" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="C17" t="s">
-        <v>18</v>
+        <v>46</v>
       </c>
       <c r="D17">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="E17" t="s">
-        <v>43</v>
+        <v>63</v>
       </c>
       <c r="F17">
-        <v>28741323</v>
+        <v>1273719</v>
       </c>
       <c r="G17" t="s">
-        <v>34</v>
+        <v>78</v>
       </c>
       <c r="H17">
-        <v>44810918</v>
+        <v>479510</v>
       </c>
     </row>
     <row r="18" spans="1:8">
@@ -953,25 +1061,25 @@
         <v>8</v>
       </c>
       <c r="B18" t="s">
-        <v>12</v>
+        <v>32</v>
       </c>
       <c r="C18" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="D18">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="E18" t="s">
-        <v>28</v>
+        <v>64</v>
       </c>
       <c r="F18">
-        <v>1747619</v>
+        <v>212042</v>
       </c>
       <c r="G18" t="s">
-        <v>29</v>
+        <v>48</v>
       </c>
       <c r="H18">
-        <v>13913874</v>
+        <v>25811332</v>
       </c>
     </row>
     <row r="19" spans="1:8">
@@ -979,25 +1087,25 @@
         <v>8</v>
       </c>
       <c r="B19" t="s">
-        <v>21</v>
+        <v>33</v>
       </c>
       <c r="C19" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="D19">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="E19" t="s">
-        <v>37</v>
+        <v>65</v>
       </c>
       <c r="F19">
-        <v>19033717</v>
+        <v>1747619</v>
       </c>
       <c r="G19" t="s">
-        <v>36</v>
+        <v>49</v>
       </c>
       <c r="H19">
-        <v>51010813</v>
+        <v>13951133</v>
       </c>
     </row>
     <row r="20" spans="1:8">
@@ -1005,25 +1113,25 @@
         <v>9</v>
       </c>
       <c r="B20" t="s">
-        <v>14</v>
+        <v>34</v>
       </c>
       <c r="C20" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="D20">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="E20" t="s">
-        <v>30</v>
+        <v>66</v>
       </c>
       <c r="F20">
         <v>20696550</v>
       </c>
       <c r="G20" t="s">
-        <v>31</v>
+        <v>50</v>
       </c>
       <c r="H20">
-        <v>117598</v>
+        <v>5823700</v>
       </c>
     </row>
     <row r="21" spans="1:8">
@@ -1031,25 +1139,25 @@
         <v>9</v>
       </c>
       <c r="B21" t="s">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="C21" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="D21">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="E21" t="s">
-        <v>39</v>
+        <v>67</v>
       </c>
       <c r="F21">
-        <v>3851966</v>
+        <v>30267301</v>
       </c>
       <c r="G21" t="s">
-        <v>38</v>
+        <v>51</v>
       </c>
       <c r="H21">
-        <v>212042</v>
+        <v>51010813</v>
       </c>
     </row>
     <row r="22" spans="1:8">
@@ -1057,25 +1165,25 @@
         <v>10</v>
       </c>
       <c r="B22" t="s">
-        <v>16</v>
+        <v>36</v>
       </c>
       <c r="C22" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="D22">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="E22" t="s">
-        <v>32</v>
+        <v>68</v>
       </c>
       <c r="F22">
-        <v>18642587</v>
+        <v>3851966</v>
       </c>
       <c r="G22" t="s">
-        <v>33</v>
+        <v>52</v>
       </c>
       <c r="H22">
-        <v>47544767</v>
+        <v>29228373</v>
       </c>
     </row>
     <row r="23" spans="1:8">
@@ -1083,25 +1191,25 @@
         <v>10</v>
       </c>
       <c r="B23" t="s">
-        <v>25</v>
+        <v>37</v>
       </c>
       <c r="C23" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="D23">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="E23" t="s">
-        <v>41</v>
+        <v>69</v>
       </c>
       <c r="F23">
-        <v>479510</v>
+        <v>7017989</v>
       </c>
       <c r="G23" t="s">
-        <v>40</v>
+        <v>53</v>
       </c>
       <c r="H23">
-        <v>387186</v>
+        <v>13913874</v>
       </c>
     </row>
     <row r="24" spans="1:8">
@@ -1109,25 +1217,25 @@
         <v>11</v>
       </c>
       <c r="B24" t="s">
-        <v>18</v>
+        <v>38</v>
       </c>
       <c r="C24" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="D24">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="E24" t="s">
-        <v>34</v>
+        <v>70</v>
       </c>
       <c r="F24">
-        <v>44810918</v>
+        <v>117598</v>
       </c>
       <c r="G24" t="s">
-        <v>35</v>
+        <v>54</v>
       </c>
       <c r="H24">
-        <v>1273719</v>
+        <v>19033717</v>
       </c>
     </row>
     <row r="25" spans="1:8">
@@ -1135,178 +1243,178 @@
         <v>11</v>
       </c>
       <c r="B25" t="s">
-        <v>27</v>
+        <v>39</v>
       </c>
       <c r="C25" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="D25">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="E25" t="s">
-        <v>43</v>
+        <v>71</v>
       </c>
       <c r="F25">
-        <v>28741323</v>
+        <v>186283</v>
       </c>
       <c r="G25" t="s">
-        <v>42</v>
+        <v>55</v>
       </c>
       <c r="H25">
-        <v>36359</v>
+        <v>24856400</v>
       </c>
     </row>
     <row r="26" spans="1:8">
       <c r="A26" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="B26" t="s">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="C26" t="s">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="D26">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="E26" t="s">
-        <v>36</v>
+        <v>72</v>
       </c>
       <c r="F26">
-        <v>51010813</v>
+        <v>36359</v>
       </c>
       <c r="G26" t="s">
-        <v>28</v>
+        <v>56</v>
       </c>
       <c r="H26">
-        <v>1747619</v>
+        <v>18642587</v>
       </c>
     </row>
     <row r="27" spans="1:8">
       <c r="A27" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="B27" t="s">
-        <v>21</v>
+        <v>41</v>
       </c>
       <c r="C27" t="s">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="D27">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="E27" t="s">
-        <v>37</v>
+        <v>73</v>
       </c>
       <c r="F27">
-        <v>19033717</v>
+        <v>14124559</v>
       </c>
       <c r="G27" t="s">
-        <v>29</v>
+        <v>57</v>
       </c>
       <c r="H27">
-        <v>13913874</v>
+        <v>18344271</v>
       </c>
     </row>
     <row r="28" spans="1:8">
       <c r="A28" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="B28" t="s">
-        <v>22</v>
+        <v>42</v>
       </c>
       <c r="C28" t="s">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="D28">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="E28" t="s">
-        <v>38</v>
+        <v>74</v>
       </c>
       <c r="F28">
-        <v>212042</v>
+        <v>44810918</v>
       </c>
       <c r="G28" t="s">
-        <v>30</v>
+        <v>59</v>
       </c>
       <c r="H28">
-        <v>20696550</v>
+        <v>387186</v>
       </c>
     </row>
     <row r="29" spans="1:8">
       <c r="A29" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="B29" t="s">
-        <v>23</v>
+        <v>43</v>
       </c>
       <c r="C29" t="s">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="D29">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="E29" t="s">
-        <v>39</v>
+        <v>75</v>
       </c>
       <c r="F29">
-        <v>3851966</v>
+        <v>18223508</v>
       </c>
       <c r="G29" t="s">
-        <v>31</v>
+        <v>58</v>
       </c>
       <c r="H29">
-        <v>117598</v>
+        <v>18346776</v>
       </c>
     </row>
     <row r="30" spans="1:8">
       <c r="A30" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="B30" t="s">
-        <v>24</v>
+        <v>44</v>
       </c>
       <c r="C30" t="s">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="D30">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="E30" t="s">
-        <v>40</v>
+        <v>76</v>
       </c>
       <c r="F30">
-        <v>387186</v>
+        <v>24468241</v>
       </c>
       <c r="G30" t="s">
-        <v>32</v>
+        <v>60</v>
       </c>
       <c r="H30">
-        <v>18642587</v>
+        <v>49355335</v>
       </c>
     </row>
     <row r="31" spans="1:8">
       <c r="A31" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="B31" t="s">
-        <v>25</v>
+        <v>45</v>
       </c>
       <c r="C31" t="s">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="D31">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="E31" t="s">
-        <v>41</v>
+        <v>77</v>
       </c>
       <c r="F31">
-        <v>479510</v>
+        <v>28741323</v>
       </c>
       <c r="G31" t="s">
-        <v>33</v>
+        <v>61</v>
       </c>
       <c r="H31">
         <v>47544767</v>
@@ -1314,51 +1422,51 @@
     </row>
     <row r="32" spans="1:8">
       <c r="A32" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="B32" t="s">
-        <v>26</v>
+        <v>46</v>
       </c>
       <c r="C32" t="s">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="D32">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="E32" t="s">
-        <v>42</v>
+        <v>78</v>
       </c>
       <c r="F32">
-        <v>36359</v>
+        <v>479510</v>
       </c>
       <c r="G32" t="s">
-        <v>34</v>
+        <v>62</v>
       </c>
       <c r="H32">
-        <v>44810918</v>
+        <v>13707047</v>
       </c>
     </row>
     <row r="33" spans="1:8">
       <c r="A33" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="B33" t="s">
-        <v>27</v>
+        <v>47</v>
       </c>
       <c r="C33" t="s">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="D33">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="E33" t="s">
-        <v>43</v>
+        <v>79</v>
       </c>
       <c r="F33">
-        <v>28741323</v>
+        <v>528730</v>
       </c>
       <c r="G33" t="s">
-        <v>35</v>
+        <v>63</v>
       </c>
       <c r="H33">
         <v>1273719</v>
@@ -1369,25 +1477,25 @@
         <v>8</v>
       </c>
       <c r="B34" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C34" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="D34">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="E34" t="s">
-        <v>29</v>
+        <v>48</v>
       </c>
       <c r="F34">
-        <v>13913874</v>
+        <v>25811332</v>
       </c>
       <c r="G34" t="s">
-        <v>36</v>
+        <v>49</v>
       </c>
       <c r="H34">
-        <v>51010813</v>
+        <v>13951133</v>
       </c>
     </row>
     <row r="35" spans="1:8">
@@ -1395,25 +1503,25 @@
         <v>8</v>
       </c>
       <c r="B35" t="s">
-        <v>12</v>
+        <v>33</v>
       </c>
       <c r="C35" t="s">
-        <v>21</v>
+        <v>32</v>
       </c>
       <c r="D35">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="E35" t="s">
-        <v>28</v>
+        <v>65</v>
       </c>
       <c r="F35">
         <v>1747619</v>
       </c>
       <c r="G35" t="s">
-        <v>37</v>
+        <v>64</v>
       </c>
       <c r="H35">
-        <v>19033717</v>
+        <v>212042</v>
       </c>
     </row>
     <row r="36" spans="1:8">
@@ -1421,25 +1529,25 @@
         <v>9</v>
       </c>
       <c r="B36" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="C36" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="D36">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="E36" t="s">
-        <v>31</v>
+        <v>50</v>
       </c>
       <c r="F36">
-        <v>117598</v>
+        <v>5823700</v>
       </c>
       <c r="G36" t="s">
-        <v>38</v>
+        <v>51</v>
       </c>
       <c r="H36">
-        <v>212042</v>
+        <v>51010813</v>
       </c>
     </row>
     <row r="37" spans="1:8">
@@ -1447,25 +1555,25 @@
         <v>9</v>
       </c>
       <c r="B37" t="s">
-        <v>14</v>
+        <v>35</v>
       </c>
       <c r="C37" t="s">
-        <v>23</v>
+        <v>34</v>
       </c>
       <c r="D37">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="E37" t="s">
-        <v>30</v>
+        <v>67</v>
       </c>
       <c r="F37">
+        <v>30267301</v>
+      </c>
+      <c r="G37" t="s">
+        <v>66</v>
+      </c>
+      <c r="H37">
         <v>20696550</v>
-      </c>
-      <c r="G37" t="s">
-        <v>39</v>
-      </c>
-      <c r="H37">
-        <v>3851966</v>
       </c>
     </row>
     <row r="38" spans="1:8">
@@ -1473,25 +1581,25 @@
         <v>10</v>
       </c>
       <c r="B38" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="C38" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="D38">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="E38" t="s">
-        <v>33</v>
+        <v>52</v>
       </c>
       <c r="F38">
-        <v>47544767</v>
+        <v>29228373</v>
       </c>
       <c r="G38" t="s">
-        <v>40</v>
+        <v>53</v>
       </c>
       <c r="H38">
-        <v>387186</v>
+        <v>13913874</v>
       </c>
     </row>
     <row r="39" spans="1:8">
@@ -1499,25 +1607,25 @@
         <v>10</v>
       </c>
       <c r="B39" t="s">
-        <v>16</v>
+        <v>37</v>
       </c>
       <c r="C39" t="s">
-        <v>25</v>
+        <v>36</v>
       </c>
       <c r="D39">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="E39" t="s">
-        <v>32</v>
+        <v>69</v>
       </c>
       <c r="F39">
-        <v>18642587</v>
+        <v>7017989</v>
       </c>
       <c r="G39" t="s">
-        <v>41</v>
+        <v>68</v>
       </c>
       <c r="H39">
-        <v>479510</v>
+        <v>3851966</v>
       </c>
     </row>
     <row r="40" spans="1:8">
@@ -1525,25 +1633,25 @@
         <v>11</v>
       </c>
       <c r="B40" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="C40" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="D40">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="E40" t="s">
-        <v>35</v>
+        <v>54</v>
       </c>
       <c r="F40">
-        <v>1273719</v>
+        <v>19033717</v>
       </c>
       <c r="G40" t="s">
-        <v>42</v>
+        <v>55</v>
       </c>
       <c r="H40">
-        <v>36359</v>
+        <v>24856400</v>
       </c>
     </row>
     <row r="41" spans="1:8">
@@ -1551,233 +1659,1481 @@
         <v>11</v>
       </c>
       <c r="B41" t="s">
-        <v>18</v>
+        <v>39</v>
       </c>
       <c r="C41" t="s">
-        <v>27</v>
+        <v>38</v>
       </c>
       <c r="D41">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="E41" t="s">
-        <v>34</v>
+        <v>71</v>
       </c>
       <c r="F41">
-        <v>44810918</v>
+        <v>186283</v>
       </c>
       <c r="G41" t="s">
-        <v>43</v>
+        <v>70</v>
       </c>
       <c r="H41">
-        <v>28741323</v>
+        <v>117598</v>
       </c>
     </row>
     <row r="42" spans="1:8">
       <c r="A42" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="B42" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="C42" t="s">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="D42">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="E42" t="s">
-        <v>29</v>
+        <v>56</v>
       </c>
       <c r="F42">
-        <v>13913874</v>
+        <v>18642587</v>
       </c>
       <c r="G42" t="s">
-        <v>28</v>
+        <v>57</v>
       </c>
       <c r="H42">
-        <v>1747619</v>
+        <v>18344271</v>
       </c>
     </row>
     <row r="43" spans="1:8">
       <c r="A43" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="B43" t="s">
-        <v>20</v>
+        <v>41</v>
       </c>
       <c r="C43" t="s">
-        <v>21</v>
+        <v>40</v>
       </c>
       <c r="D43">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="E43" t="s">
-        <v>36</v>
+        <v>73</v>
       </c>
       <c r="F43">
-        <v>51010813</v>
+        <v>14124559</v>
       </c>
       <c r="G43" t="s">
-        <v>37</v>
+        <v>72</v>
       </c>
       <c r="H43">
-        <v>19033717</v>
+        <v>36359</v>
       </c>
     </row>
     <row r="44" spans="1:8">
       <c r="A44" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="B44" t="s">
-        <v>15</v>
+        <v>42</v>
       </c>
       <c r="C44" t="s">
-        <v>14</v>
+        <v>43</v>
       </c>
       <c r="D44">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="E44" t="s">
-        <v>31</v>
+        <v>74</v>
       </c>
       <c r="F44">
-        <v>117598</v>
+        <v>44810918</v>
       </c>
       <c r="G44" t="s">
-        <v>30</v>
+        <v>75</v>
       </c>
       <c r="H44">
-        <v>20696550</v>
+        <v>18223508</v>
       </c>
     </row>
     <row r="45" spans="1:8">
       <c r="A45" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="B45" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="C45" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="D45">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="E45" t="s">
-        <v>38</v>
+        <v>58</v>
       </c>
       <c r="F45">
-        <v>212042</v>
+        <v>18346776</v>
       </c>
       <c r="G45" t="s">
-        <v>39</v>
+        <v>59</v>
       </c>
       <c r="H45">
-        <v>3851966</v>
+        <v>387186</v>
       </c>
     </row>
     <row r="46" spans="1:8">
       <c r="A46" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="B46" t="s">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="C46" t="s">
-        <v>16</v>
+        <v>29</v>
       </c>
       <c r="D46">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="E46" t="s">
-        <v>33</v>
+        <v>60</v>
       </c>
       <c r="F46">
+        <v>49355335</v>
+      </c>
+      <c r="G46" t="s">
+        <v>61</v>
+      </c>
+      <c r="H46">
         <v>47544767</v>
-      </c>
-      <c r="G46" t="s">
-        <v>32</v>
-      </c>
-      <c r="H46">
-        <v>18642587</v>
       </c>
     </row>
     <row r="47" spans="1:8">
       <c r="A47" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="B47" t="s">
-        <v>24</v>
+        <v>45</v>
       </c>
       <c r="C47" t="s">
-        <v>25</v>
+        <v>44</v>
       </c>
       <c r="D47">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="E47" t="s">
-        <v>40</v>
+        <v>77</v>
       </c>
       <c r="F47">
-        <v>387186</v>
+        <v>28741323</v>
       </c>
       <c r="G47" t="s">
-        <v>41</v>
+        <v>76</v>
       </c>
       <c r="H47">
-        <v>479510</v>
+        <v>24468241</v>
       </c>
     </row>
     <row r="48" spans="1:8">
       <c r="A48" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="B48" t="s">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="C48" t="s">
-        <v>18</v>
+        <v>31</v>
       </c>
       <c r="D48">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="E48" t="s">
-        <v>35</v>
+        <v>62</v>
       </c>
       <c r="F48">
+        <v>13707047</v>
+      </c>
+      <c r="G48" t="s">
+        <v>63</v>
+      </c>
+      <c r="H48">
         <v>1273719</v>
-      </c>
-      <c r="G48" t="s">
-        <v>34</v>
-      </c>
-      <c r="H48">
-        <v>44810918</v>
       </c>
     </row>
     <row r="49" spans="1:8">
       <c r="A49" t="s">
+        <v>15</v>
+      </c>
+      <c r="B49" t="s">
+        <v>47</v>
+      </c>
+      <c r="C49" t="s">
+        <v>46</v>
+      </c>
+      <c r="D49">
+        <v>3</v>
+      </c>
+      <c r="E49" t="s">
+        <v>79</v>
+      </c>
+      <c r="F49">
+        <v>528730</v>
+      </c>
+      <c r="G49" t="s">
+        <v>78</v>
+      </c>
+      <c r="H49">
+        <v>479510</v>
+      </c>
+    </row>
+    <row r="50" spans="1:8">
+      <c r="A50" t="s">
+        <v>8</v>
+      </c>
+      <c r="B50" t="s">
+        <v>16</v>
+      </c>
+      <c r="C50" t="s">
+        <v>32</v>
+      </c>
+      <c r="D50">
+        <v>4</v>
+      </c>
+      <c r="E50" t="s">
+        <v>48</v>
+      </c>
+      <c r="F50">
+        <v>25811332</v>
+      </c>
+      <c r="G50" t="s">
+        <v>64</v>
+      </c>
+      <c r="H50">
+        <v>212042</v>
+      </c>
+    </row>
+    <row r="51" spans="1:8">
+      <c r="A51" t="s">
+        <v>8</v>
+      </c>
+      <c r="B51" t="s">
+        <v>17</v>
+      </c>
+      <c r="C51" t="s">
+        <v>33</v>
+      </c>
+      <c r="D51">
+        <v>4</v>
+      </c>
+      <c r="E51" t="s">
+        <v>49</v>
+      </c>
+      <c r="F51">
+        <v>13951133</v>
+      </c>
+      <c r="G51" t="s">
+        <v>65</v>
+      </c>
+      <c r="H51">
+        <v>1747619</v>
+      </c>
+    </row>
+    <row r="52" spans="1:8">
+      <c r="A52" t="s">
+        <v>9</v>
+      </c>
+      <c r="B52" t="s">
+        <v>18</v>
+      </c>
+      <c r="C52" t="s">
+        <v>34</v>
+      </c>
+      <c r="D52">
+        <v>4</v>
+      </c>
+      <c r="E52" t="s">
+        <v>50</v>
+      </c>
+      <c r="F52">
+        <v>5823700</v>
+      </c>
+      <c r="G52" t="s">
+        <v>66</v>
+      </c>
+      <c r="H52">
+        <v>20696550</v>
+      </c>
+    </row>
+    <row r="53" spans="1:8">
+      <c r="A53" t="s">
+        <v>9</v>
+      </c>
+      <c r="B53" t="s">
+        <v>19</v>
+      </c>
+      <c r="C53" t="s">
+        <v>35</v>
+      </c>
+      <c r="D53">
+        <v>4</v>
+      </c>
+      <c r="E53" t="s">
+        <v>51</v>
+      </c>
+      <c r="F53">
+        <v>51010813</v>
+      </c>
+      <c r="G53" t="s">
+        <v>67</v>
+      </c>
+      <c r="H53">
+        <v>30267301</v>
+      </c>
+    </row>
+    <row r="54" spans="1:8">
+      <c r="A54" t="s">
+        <v>10</v>
+      </c>
+      <c r="B54" t="s">
+        <v>20</v>
+      </c>
+      <c r="C54" t="s">
+        <v>36</v>
+      </c>
+      <c r="D54">
+        <v>4</v>
+      </c>
+      <c r="E54" t="s">
+        <v>52</v>
+      </c>
+      <c r="F54">
+        <v>29228373</v>
+      </c>
+      <c r="G54" t="s">
+        <v>68</v>
+      </c>
+      <c r="H54">
+        <v>3851966</v>
+      </c>
+    </row>
+    <row r="55" spans="1:8">
+      <c r="A55" t="s">
+        <v>10</v>
+      </c>
+      <c r="B55" t="s">
+        <v>21</v>
+      </c>
+      <c r="C55" t="s">
+        <v>37</v>
+      </c>
+      <c r="D55">
+        <v>4</v>
+      </c>
+      <c r="E55" t="s">
+        <v>53</v>
+      </c>
+      <c r="F55">
+        <v>13913874</v>
+      </c>
+      <c r="G55" t="s">
+        <v>69</v>
+      </c>
+      <c r="H55">
+        <v>7017989</v>
+      </c>
+    </row>
+    <row r="56" spans="1:8">
+      <c r="A56" t="s">
         <v>11</v>
       </c>
-      <c r="B49" t="s">
+      <c r="B56" t="s">
+        <v>22</v>
+      </c>
+      <c r="C56" t="s">
+        <v>38</v>
+      </c>
+      <c r="D56">
+        <v>4</v>
+      </c>
+      <c r="E56" t="s">
+        <v>54</v>
+      </c>
+      <c r="F56">
+        <v>19033717</v>
+      </c>
+      <c r="G56" t="s">
+        <v>70</v>
+      </c>
+      <c r="H56">
+        <v>117598</v>
+      </c>
+    </row>
+    <row r="57" spans="1:8">
+      <c r="A57" t="s">
+        <v>11</v>
+      </c>
+      <c r="B57" t="s">
+        <v>23</v>
+      </c>
+      <c r="C57" t="s">
+        <v>39</v>
+      </c>
+      <c r="D57">
+        <v>4</v>
+      </c>
+      <c r="E57" t="s">
+        <v>55</v>
+      </c>
+      <c r="F57">
+        <v>24856400</v>
+      </c>
+      <c r="G57" t="s">
+        <v>71</v>
+      </c>
+      <c r="H57">
+        <v>186283</v>
+      </c>
+    </row>
+    <row r="58" spans="1:8">
+      <c r="A58" t="s">
+        <v>12</v>
+      </c>
+      <c r="B58" t="s">
+        <v>24</v>
+      </c>
+      <c r="C58" t="s">
+        <v>40</v>
+      </c>
+      <c r="D58">
+        <v>4</v>
+      </c>
+      <c r="E58" t="s">
+        <v>56</v>
+      </c>
+      <c r="F58">
+        <v>18642587</v>
+      </c>
+      <c r="G58" t="s">
+        <v>72</v>
+      </c>
+      <c r="H58">
+        <v>36359</v>
+      </c>
+    </row>
+    <row r="59" spans="1:8">
+      <c r="A59" t="s">
+        <v>12</v>
+      </c>
+      <c r="B59" t="s">
+        <v>25</v>
+      </c>
+      <c r="C59" t="s">
+        <v>41</v>
+      </c>
+      <c r="D59">
+        <v>4</v>
+      </c>
+      <c r="E59" t="s">
+        <v>57</v>
+      </c>
+      <c r="F59">
+        <v>18344271</v>
+      </c>
+      <c r="G59" t="s">
+        <v>73</v>
+      </c>
+      <c r="H59">
+        <v>14124559</v>
+      </c>
+    </row>
+    <row r="60" spans="1:8">
+      <c r="A60" t="s">
+        <v>13</v>
+      </c>
+      <c r="B60" t="s">
+        <v>27</v>
+      </c>
+      <c r="C60" t="s">
+        <v>42</v>
+      </c>
+      <c r="D60">
+        <v>4</v>
+      </c>
+      <c r="E60" t="s">
+        <v>59</v>
+      </c>
+      <c r="F60">
+        <v>387186</v>
+      </c>
+      <c r="G60" t="s">
+        <v>74</v>
+      </c>
+      <c r="H60">
+        <v>44810918</v>
+      </c>
+    </row>
+    <row r="61" spans="1:8">
+      <c r="A61" t="s">
+        <v>13</v>
+      </c>
+      <c r="B61" t="s">
         <v>26</v>
       </c>
-      <c r="C49" t="s">
+      <c r="C61" t="s">
+        <v>43</v>
+      </c>
+      <c r="D61">
+        <v>4</v>
+      </c>
+      <c r="E61" t="s">
+        <v>58</v>
+      </c>
+      <c r="F61">
+        <v>18346776</v>
+      </c>
+      <c r="G61" t="s">
+        <v>75</v>
+      </c>
+      <c r="H61">
+        <v>18223508</v>
+      </c>
+    </row>
+    <row r="62" spans="1:8">
+      <c r="A62" t="s">
+        <v>14</v>
+      </c>
+      <c r="B62" t="s">
+        <v>28</v>
+      </c>
+      <c r="C62" t="s">
+        <v>44</v>
+      </c>
+      <c r="D62">
+        <v>4</v>
+      </c>
+      <c r="E62" t="s">
+        <v>60</v>
+      </c>
+      <c r="F62">
+        <v>49355335</v>
+      </c>
+      <c r="G62" t="s">
+        <v>76</v>
+      </c>
+      <c r="H62">
+        <v>24468241</v>
+      </c>
+    </row>
+    <row r="63" spans="1:8">
+      <c r="A63" t="s">
+        <v>14</v>
+      </c>
+      <c r="B63" t="s">
+        <v>29</v>
+      </c>
+      <c r="C63" t="s">
+        <v>45</v>
+      </c>
+      <c r="D63">
+        <v>4</v>
+      </c>
+      <c r="E63" t="s">
+        <v>61</v>
+      </c>
+      <c r="F63">
+        <v>47544767</v>
+      </c>
+      <c r="G63" t="s">
+        <v>77</v>
+      </c>
+      <c r="H63">
+        <v>28741323</v>
+      </c>
+    </row>
+    <row r="64" spans="1:8">
+      <c r="A64" t="s">
+        <v>15</v>
+      </c>
+      <c r="B64" t="s">
+        <v>30</v>
+      </c>
+      <c r="C64" t="s">
+        <v>46</v>
+      </c>
+      <c r="D64">
+        <v>4</v>
+      </c>
+      <c r="E64" t="s">
+        <v>62</v>
+      </c>
+      <c r="F64">
+        <v>13707047</v>
+      </c>
+      <c r="G64" t="s">
+        <v>78</v>
+      </c>
+      <c r="H64">
+        <v>479510</v>
+      </c>
+    </row>
+    <row r="65" spans="1:8">
+      <c r="A65" t="s">
+        <v>15</v>
+      </c>
+      <c r="B65" t="s">
+        <v>31</v>
+      </c>
+      <c r="C65" t="s">
+        <v>47</v>
+      </c>
+      <c r="D65">
+        <v>4</v>
+      </c>
+      <c r="E65" t="s">
+        <v>63</v>
+      </c>
+      <c r="F65">
+        <v>1273719</v>
+      </c>
+      <c r="G65" t="s">
+        <v>79</v>
+      </c>
+      <c r="H65">
+        <v>528730</v>
+      </c>
+    </row>
+    <row r="66" spans="1:8">
+      <c r="A66" t="s">
+        <v>8</v>
+      </c>
+      <c r="B66" t="s">
+        <v>17</v>
+      </c>
+      <c r="C66" t="s">
+        <v>16</v>
+      </c>
+      <c r="D66">
+        <v>5</v>
+      </c>
+      <c r="E66" t="s">
+        <v>49</v>
+      </c>
+      <c r="F66">
+        <v>13951133</v>
+      </c>
+      <c r="G66" t="s">
+        <v>48</v>
+      </c>
+      <c r="H66">
+        <v>25811332</v>
+      </c>
+    </row>
+    <row r="67" spans="1:8">
+      <c r="A67" t="s">
+        <v>8</v>
+      </c>
+      <c r="B67" t="s">
+        <v>32</v>
+      </c>
+      <c r="C67" t="s">
+        <v>33</v>
+      </c>
+      <c r="D67">
+        <v>5</v>
+      </c>
+      <c r="E67" t="s">
+        <v>64</v>
+      </c>
+      <c r="F67">
+        <v>212042</v>
+      </c>
+      <c r="G67" t="s">
+        <v>65</v>
+      </c>
+      <c r="H67">
+        <v>1747619</v>
+      </c>
+    </row>
+    <row r="68" spans="1:8">
+      <c r="A68" t="s">
+        <v>9</v>
+      </c>
+      <c r="B68" t="s">
+        <v>19</v>
+      </c>
+      <c r="C68" t="s">
+        <v>18</v>
+      </c>
+      <c r="D68">
+        <v>5</v>
+      </c>
+      <c r="E68" t="s">
+        <v>51</v>
+      </c>
+      <c r="F68">
+        <v>51010813</v>
+      </c>
+      <c r="G68" t="s">
+        <v>50</v>
+      </c>
+      <c r="H68">
+        <v>5823700</v>
+      </c>
+    </row>
+    <row r="69" spans="1:8">
+      <c r="A69" t="s">
+        <v>9</v>
+      </c>
+      <c r="B69" t="s">
+        <v>34</v>
+      </c>
+      <c r="C69" t="s">
+        <v>35</v>
+      </c>
+      <c r="D69">
+        <v>5</v>
+      </c>
+      <c r="E69" t="s">
+        <v>66</v>
+      </c>
+      <c r="F69">
+        <v>20696550</v>
+      </c>
+      <c r="G69" t="s">
+        <v>67</v>
+      </c>
+      <c r="H69">
+        <v>30267301</v>
+      </c>
+    </row>
+    <row r="70" spans="1:8">
+      <c r="A70" t="s">
+        <v>10</v>
+      </c>
+      <c r="B70" t="s">
+        <v>21</v>
+      </c>
+      <c r="C70" t="s">
+        <v>20</v>
+      </c>
+      <c r="D70">
+        <v>5</v>
+      </c>
+      <c r="E70" t="s">
+        <v>53</v>
+      </c>
+      <c r="F70">
+        <v>13913874</v>
+      </c>
+      <c r="G70" t="s">
+        <v>52</v>
+      </c>
+      <c r="H70">
+        <v>29228373</v>
+      </c>
+    </row>
+    <row r="71" spans="1:8">
+      <c r="A71" t="s">
+        <v>10</v>
+      </c>
+      <c r="B71" t="s">
+        <v>36</v>
+      </c>
+      <c r="C71" t="s">
+        <v>37</v>
+      </c>
+      <c r="D71">
+        <v>5</v>
+      </c>
+      <c r="E71" t="s">
+        <v>68</v>
+      </c>
+      <c r="F71">
+        <v>3851966</v>
+      </c>
+      <c r="G71" t="s">
+        <v>69</v>
+      </c>
+      <c r="H71">
+        <v>7017989</v>
+      </c>
+    </row>
+    <row r="72" spans="1:8">
+      <c r="A72" t="s">
+        <v>11</v>
+      </c>
+      <c r="B72" t="s">
+        <v>23</v>
+      </c>
+      <c r="C72" t="s">
+        <v>22</v>
+      </c>
+      <c r="D72">
+        <v>5</v>
+      </c>
+      <c r="E72" t="s">
+        <v>55</v>
+      </c>
+      <c r="F72">
+        <v>24856400</v>
+      </c>
+      <c r="G72" t="s">
+        <v>54</v>
+      </c>
+      <c r="H72">
+        <v>19033717</v>
+      </c>
+    </row>
+    <row r="73" spans="1:8">
+      <c r="A73" t="s">
+        <v>11</v>
+      </c>
+      <c r="B73" t="s">
+        <v>38</v>
+      </c>
+      <c r="C73" t="s">
+        <v>39</v>
+      </c>
+      <c r="D73">
+        <v>5</v>
+      </c>
+      <c r="E73" t="s">
+        <v>70</v>
+      </c>
+      <c r="F73">
+        <v>117598</v>
+      </c>
+      <c r="G73" t="s">
+        <v>71</v>
+      </c>
+      <c r="H73">
+        <v>186283</v>
+      </c>
+    </row>
+    <row r="74" spans="1:8">
+      <c r="A74" t="s">
+        <v>12</v>
+      </c>
+      <c r="B74" t="s">
+        <v>25</v>
+      </c>
+      <c r="C74" t="s">
+        <v>24</v>
+      </c>
+      <c r="D74">
+        <v>5</v>
+      </c>
+      <c r="E74" t="s">
+        <v>57</v>
+      </c>
+      <c r="F74">
+        <v>18344271</v>
+      </c>
+      <c r="G74" t="s">
+        <v>56</v>
+      </c>
+      <c r="H74">
+        <v>18642587</v>
+      </c>
+    </row>
+    <row r="75" spans="1:8">
+      <c r="A75" t="s">
+        <v>12</v>
+      </c>
+      <c r="B75" t="s">
+        <v>40</v>
+      </c>
+      <c r="C75" t="s">
+        <v>41</v>
+      </c>
+      <c r="D75">
+        <v>5</v>
+      </c>
+      <c r="E75" t="s">
+        <v>72</v>
+      </c>
+      <c r="F75">
+        <v>36359</v>
+      </c>
+      <c r="G75" t="s">
+        <v>73</v>
+      </c>
+      <c r="H75">
+        <v>14124559</v>
+      </c>
+    </row>
+    <row r="76" spans="1:8">
+      <c r="A76" t="s">
+        <v>13</v>
+      </c>
+      <c r="B76" t="s">
+        <v>43</v>
+      </c>
+      <c r="C76" t="s">
+        <v>42</v>
+      </c>
+      <c r="D76">
+        <v>5</v>
+      </c>
+      <c r="E76" t="s">
+        <v>75</v>
+      </c>
+      <c r="F76">
+        <v>18223508</v>
+      </c>
+      <c r="G76" t="s">
+        <v>74</v>
+      </c>
+      <c r="H76">
+        <v>44810918</v>
+      </c>
+    </row>
+    <row r="77" spans="1:8">
+      <c r="A77" t="s">
+        <v>13</v>
+      </c>
+      <c r="B77" t="s">
         <v>27</v>
       </c>
-      <c r="D49">
+      <c r="C77" t="s">
+        <v>26</v>
+      </c>
+      <c r="D77">
+        <v>5</v>
+      </c>
+      <c r="E77" t="s">
+        <v>59</v>
+      </c>
+      <c r="F77">
+        <v>387186</v>
+      </c>
+      <c r="G77" t="s">
+        <v>58</v>
+      </c>
+      <c r="H77">
+        <v>18346776</v>
+      </c>
+    </row>
+    <row r="78" spans="1:8">
+      <c r="A78" t="s">
+        <v>14</v>
+      </c>
+      <c r="B78" t="s">
+        <v>29</v>
+      </c>
+      <c r="C78" t="s">
+        <v>28</v>
+      </c>
+      <c r="D78">
+        <v>5</v>
+      </c>
+      <c r="E78" t="s">
+        <v>61</v>
+      </c>
+      <c r="F78">
+        <v>47544767</v>
+      </c>
+      <c r="G78" t="s">
+        <v>60</v>
+      </c>
+      <c r="H78">
+        <v>49355335</v>
+      </c>
+    </row>
+    <row r="79" spans="1:8">
+      <c r="A79" t="s">
+        <v>14</v>
+      </c>
+      <c r="B79" t="s">
+        <v>44</v>
+      </c>
+      <c r="C79" t="s">
+        <v>45</v>
+      </c>
+      <c r="D79">
+        <v>5</v>
+      </c>
+      <c r="E79" t="s">
+        <v>76</v>
+      </c>
+      <c r="F79">
+        <v>24468241</v>
+      </c>
+      <c r="G79" t="s">
+        <v>77</v>
+      </c>
+      <c r="H79">
+        <v>28741323</v>
+      </c>
+    </row>
+    <row r="80" spans="1:8">
+      <c r="A80" t="s">
+        <v>15</v>
+      </c>
+      <c r="B80" t="s">
+        <v>31</v>
+      </c>
+      <c r="C80" t="s">
+        <v>30</v>
+      </c>
+      <c r="D80">
+        <v>5</v>
+      </c>
+      <c r="E80" t="s">
+        <v>63</v>
+      </c>
+      <c r="F80">
+        <v>1273719</v>
+      </c>
+      <c r="G80" t="s">
+        <v>62</v>
+      </c>
+      <c r="H80">
+        <v>13707047</v>
+      </c>
+    </row>
+    <row r="81" spans="1:8">
+      <c r="A81" t="s">
+        <v>15</v>
+      </c>
+      <c r="B81" t="s">
+        <v>46</v>
+      </c>
+      <c r="C81" t="s">
+        <v>47</v>
+      </c>
+      <c r="D81">
+        <v>5</v>
+      </c>
+      <c r="E81" t="s">
+        <v>78</v>
+      </c>
+      <c r="F81">
+        <v>479510</v>
+      </c>
+      <c r="G81" t="s">
+        <v>79</v>
+      </c>
+      <c r="H81">
+        <v>528730</v>
+      </c>
+    </row>
+    <row r="82" spans="1:8">
+      <c r="A82" t="s">
+        <v>8</v>
+      </c>
+      <c r="B82" t="s">
+        <v>32</v>
+      </c>
+      <c r="C82" t="s">
+        <v>17</v>
+      </c>
+      <c r="D82">
+        <v>6</v>
+      </c>
+      <c r="E82" t="s">
+        <v>64</v>
+      </c>
+      <c r="F82">
+        <v>212042</v>
+      </c>
+      <c r="G82" t="s">
+        <v>49</v>
+      </c>
+      <c r="H82">
+        <v>13951133</v>
+      </c>
+    </row>
+    <row r="83" spans="1:8">
+      <c r="A83" t="s">
+        <v>8</v>
+      </c>
+      <c r="B83" t="s">
+        <v>33</v>
+      </c>
+      <c r="C83" t="s">
+        <v>16</v>
+      </c>
+      <c r="D83">
+        <v>6</v>
+      </c>
+      <c r="E83" t="s">
+        <v>65</v>
+      </c>
+      <c r="F83">
+        <v>1747619</v>
+      </c>
+      <c r="G83" t="s">
+        <v>48</v>
+      </c>
+      <c r="H83">
+        <v>25811332</v>
+      </c>
+    </row>
+    <row r="84" spans="1:8">
+      <c r="A84" t="s">
+        <v>9</v>
+      </c>
+      <c r="B84" t="s">
+        <v>34</v>
+      </c>
+      <c r="C84" t="s">
+        <v>19</v>
+      </c>
+      <c r="D84">
+        <v>6</v>
+      </c>
+      <c r="E84" t="s">
+        <v>66</v>
+      </c>
+      <c r="F84">
+        <v>20696550</v>
+      </c>
+      <c r="G84" t="s">
+        <v>51</v>
+      </c>
+      <c r="H84">
+        <v>51010813</v>
+      </c>
+    </row>
+    <row r="85" spans="1:8">
+      <c r="A85" t="s">
+        <v>9</v>
+      </c>
+      <c r="B85" t="s">
+        <v>35</v>
+      </c>
+      <c r="C85" t="s">
+        <v>18</v>
+      </c>
+      <c r="D85">
+        <v>6</v>
+      </c>
+      <c r="E85" t="s">
+        <v>67</v>
+      </c>
+      <c r="F85">
+        <v>30267301</v>
+      </c>
+      <c r="G85" t="s">
+        <v>50</v>
+      </c>
+      <c r="H85">
+        <v>5823700</v>
+      </c>
+    </row>
+    <row r="86" spans="1:8">
+      <c r="A86" t="s">
+        <v>10</v>
+      </c>
+      <c r="B86" t="s">
+        <v>36</v>
+      </c>
+      <c r="C86" t="s">
+        <v>21</v>
+      </c>
+      <c r="D86">
+        <v>6</v>
+      </c>
+      <c r="E86" t="s">
+        <v>68</v>
+      </c>
+      <c r="F86">
+        <v>3851966</v>
+      </c>
+      <c r="G86" t="s">
+        <v>53</v>
+      </c>
+      <c r="H86">
+        <v>13913874</v>
+      </c>
+    </row>
+    <row r="87" spans="1:8">
+      <c r="A87" t="s">
+        <v>10</v>
+      </c>
+      <c r="B87" t="s">
+        <v>37</v>
+      </c>
+      <c r="C87" t="s">
+        <v>20</v>
+      </c>
+      <c r="D87">
+        <v>6</v>
+      </c>
+      <c r="E87" t="s">
+        <v>69</v>
+      </c>
+      <c r="F87">
+        <v>7017989</v>
+      </c>
+      <c r="G87" t="s">
+        <v>52</v>
+      </c>
+      <c r="H87">
+        <v>29228373</v>
+      </c>
+    </row>
+    <row r="88" spans="1:8">
+      <c r="A88" t="s">
+        <v>11</v>
+      </c>
+      <c r="B88" t="s">
+        <v>38</v>
+      </c>
+      <c r="C88" t="s">
+        <v>23</v>
+      </c>
+      <c r="D88">
+        <v>6</v>
+      </c>
+      <c r="E88" t="s">
+        <v>70</v>
+      </c>
+      <c r="F88">
+        <v>117598</v>
+      </c>
+      <c r="G88" t="s">
+        <v>55</v>
+      </c>
+      <c r="H88">
+        <v>24856400</v>
+      </c>
+    </row>
+    <row r="89" spans="1:8">
+      <c r="A89" t="s">
+        <v>11</v>
+      </c>
+      <c r="B89" t="s">
+        <v>39</v>
+      </c>
+      <c r="C89" t="s">
+        <v>22</v>
+      </c>
+      <c r="D89">
+        <v>6</v>
+      </c>
+      <c r="E89" t="s">
+        <v>71</v>
+      </c>
+      <c r="F89">
+        <v>186283</v>
+      </c>
+      <c r="G89" t="s">
+        <v>54</v>
+      </c>
+      <c r="H89">
+        <v>19033717</v>
+      </c>
+    </row>
+    <row r="90" spans="1:8">
+      <c r="A90" t="s">
         <v>12</v>
       </c>
-      <c r="E49" t="s">
+      <c r="B90" t="s">
+        <v>40</v>
+      </c>
+      <c r="C90" t="s">
+        <v>25</v>
+      </c>
+      <c r="D90">
+        <v>6</v>
+      </c>
+      <c r="E90" t="s">
+        <v>72</v>
+      </c>
+      <c r="F90">
+        <v>36359</v>
+      </c>
+      <c r="G90" t="s">
+        <v>57</v>
+      </c>
+      <c r="H90">
+        <v>18344271</v>
+      </c>
+    </row>
+    <row r="91" spans="1:8">
+      <c r="A91" t="s">
+        <v>12</v>
+      </c>
+      <c r="B91" t="s">
+        <v>41</v>
+      </c>
+      <c r="C91" t="s">
+        <v>24</v>
+      </c>
+      <c r="D91">
+        <v>6</v>
+      </c>
+      <c r="E91" t="s">
+        <v>73</v>
+      </c>
+      <c r="F91">
+        <v>14124559</v>
+      </c>
+      <c r="G91" t="s">
+        <v>56</v>
+      </c>
+      <c r="H91">
+        <v>18642587</v>
+      </c>
+    </row>
+    <row r="92" spans="1:8">
+      <c r="A92" t="s">
+        <v>13</v>
+      </c>
+      <c r="B92" t="s">
+        <v>43</v>
+      </c>
+      <c r="C92" t="s">
+        <v>27</v>
+      </c>
+      <c r="D92">
+        <v>6</v>
+      </c>
+      <c r="E92" t="s">
+        <v>75</v>
+      </c>
+      <c r="F92">
+        <v>18223508</v>
+      </c>
+      <c r="G92" t="s">
+        <v>59</v>
+      </c>
+      <c r="H92">
+        <v>387186</v>
+      </c>
+    </row>
+    <row r="93" spans="1:8">
+      <c r="A93" t="s">
+        <v>13</v>
+      </c>
+      <c r="B93" t="s">
         <v>42</v>
       </c>
-      <c r="F49">
-        <v>36359</v>
-      </c>
-      <c r="G49" t="s">
-        <v>43</v>
-      </c>
-      <c r="H49">
+      <c r="C93" t="s">
+        <v>26</v>
+      </c>
+      <c r="D93">
+        <v>6</v>
+      </c>
+      <c r="E93" t="s">
+        <v>74</v>
+      </c>
+      <c r="F93">
+        <v>44810918</v>
+      </c>
+      <c r="G93" t="s">
+        <v>58</v>
+      </c>
+      <c r="H93">
+        <v>18346776</v>
+      </c>
+    </row>
+    <row r="94" spans="1:8">
+      <c r="A94" t="s">
+        <v>14</v>
+      </c>
+      <c r="B94" t="s">
+        <v>44</v>
+      </c>
+      <c r="C94" t="s">
+        <v>29</v>
+      </c>
+      <c r="D94">
+        <v>6</v>
+      </c>
+      <c r="E94" t="s">
+        <v>76</v>
+      </c>
+      <c r="F94">
+        <v>24468241</v>
+      </c>
+      <c r="G94" t="s">
+        <v>61</v>
+      </c>
+      <c r="H94">
+        <v>47544767</v>
+      </c>
+    </row>
+    <row r="95" spans="1:8">
+      <c r="A95" t="s">
+        <v>14</v>
+      </c>
+      <c r="B95" t="s">
+        <v>45</v>
+      </c>
+      <c r="C95" t="s">
+        <v>28</v>
+      </c>
+      <c r="D95">
+        <v>6</v>
+      </c>
+      <c r="E95" t="s">
+        <v>77</v>
+      </c>
+      <c r="F95">
         <v>28741323</v>
+      </c>
+      <c r="G95" t="s">
+        <v>60</v>
+      </c>
+      <c r="H95">
+        <v>49355335</v>
+      </c>
+    </row>
+    <row r="96" spans="1:8">
+      <c r="A96" t="s">
+        <v>15</v>
+      </c>
+      <c r="B96" t="s">
+        <v>46</v>
+      </c>
+      <c r="C96" t="s">
+        <v>31</v>
+      </c>
+      <c r="D96">
+        <v>6</v>
+      </c>
+      <c r="E96" t="s">
+        <v>78</v>
+      </c>
+      <c r="F96">
+        <v>479510</v>
+      </c>
+      <c r="G96" t="s">
+        <v>63</v>
+      </c>
+      <c r="H96">
+        <v>1273719</v>
+      </c>
+    </row>
+    <row r="97" spans="1:8">
+      <c r="A97" t="s">
+        <v>15</v>
+      </c>
+      <c r="B97" t="s">
+        <v>47</v>
+      </c>
+      <c r="C97" t="s">
+        <v>30</v>
+      </c>
+      <c r="D97">
+        <v>6</v>
+      </c>
+      <c r="E97" t="s">
+        <v>79</v>
+      </c>
+      <c r="F97">
+        <v>528730</v>
+      </c>
+      <c r="G97" t="s">
+        <v>62</v>
+      </c>
+      <c r="H97">
+        <v>13707047</v>
       </c>
     </row>
   </sheetData>
